--- a/tests/fixtures/sample_dataset.xlsx
+++ b/tests/fixtures/sample_dataset.xlsx
@@ -624,11 +624,7 @@
           <t>https://doi.org/10.1016/j.knosys.2021.100004</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Fraudulent transactions represent a tiny fraction of payment traffic, which makes anomaly detectors prone to majority-class bias. We compare resampling, cost-sensitive learning, and synthetic minority oversampling, and report that cost-sensitive objectives give the most stable precision-recall trade-off in production settings.</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>class imbalance; anomaly detection; SMOTE</t>
@@ -710,11 +706,7 @@
           <t>https://doi.org/10.1109/ACCESS.2020.100006</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Payment systems form dense transaction graphs whose structure carries signal about coordinated abuse. We apply graph neural networks to inter-account transfer graphs and detect collusive rings that node-level classifiers miss entirely.</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>graph neural networks; payment networks; collusion</t>
@@ -839,11 +831,7 @@
           <t>https://doi.org/10.1016/j.patrec.2021.100009</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Accuracy is misleading when the positive class is rare. We formalise the relationship between precision-recall area and cost-weighted utility, and recommend reporting partial AUC at operationally relevant false positive rates.</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>evaluation metrics; imbalanced data; precision-recall</t>
